--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484802_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484802_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8284</v>
+        <v>5.1614</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7068</v>
+        <v>4.9604</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1217</v>
+        <v>0.201</v>
       </c>
       <c r="G2" t="n">
         <v>4.1674</v>
@@ -610,13 +610,13 @@
         <v>0.3774</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0182</v>
+        <v>0.3148</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2939</v>
+        <v>-0.0403</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2757</v>
+        <v>0.3551</v>
       </c>
       <c r="V2" t="n">
         <v>0.3018</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6445</v>
+        <v>4.8285</v>
       </c>
       <c r="E3" t="n">
-        <v>3.206</v>
+        <v>3.6545</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4385</v>
+        <v>1.174</v>
       </c>
       <c r="G3" t="n">
         <v>1.1341</v>
@@ -688,13 +688,13 @@
         <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1147</v>
+        <v>0.2987</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.117</v>
+        <v>-0.6684</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2316</v>
+        <v>0.9671</v>
       </c>
       <c r="V3" t="n">
         <v>4.3392</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1842</v>
+        <v>1.7545</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2686</v>
+        <v>3.5479</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0844</v>
+        <v>-1.7934</v>
       </c>
       <c r="G4" t="n">
         <v>0.325</v>
@@ -766,13 +766,13 @@
         <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1992</v>
+        <v>0.7695</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0081</v>
+        <v>0.2874</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1911</v>
+        <v>0.4821</v>
       </c>
       <c r="V4" t="n">
         <v>2.1696</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>L. SCOTT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.063</v>
+        <v>-0.4198</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2032</v>
+        <v>-0.4773</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2662</v>
+        <v>0.0575</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7635</v>
+        <v>0.2817</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.8961</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1319</v>
+        <v>1.1777</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2649</v>
+        <v>0.7215</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.306</v>
+        <v>0.0634</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0411</v>
+        <v>0.6581</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4986</v>
+        <v>-0.4398</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3256</v>
+        <v>-0.9595</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.173</v>
+        <v>0.5196</v>
       </c>
       <c r="P6" t="n">
         <v>-0.5661</v>
@@ -922,13 +922,13 @@
         <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3926</v>
+        <v>-0.1354</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0052</v>
+        <v>-0.2553</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3874</v>
+        <v>0.1199</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SCOTT</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4908</v>
+        <v>-0.7248</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5748</v>
+        <v>-0.8852</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.1604</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2817</v>
+        <v>-0.7635</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8961</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1777</v>
+        <v>-0.1319</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7215</v>
+        <v>-0.2649</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0634</v>
+        <v>-0.306</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6581</v>
+        <v>0.0411</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4398</v>
+        <v>-0.4986</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9595</v>
+        <v>-0.3256</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5196</v>
+        <v>-0.173</v>
       </c>
       <c r="P7" t="n">
         <v>-0.5661</v>
@@ -1000,13 +1000,13 @@
         <v>0.3774</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2063</v>
+        <v>0.6047</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3527</v>
+        <v>0.3231</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1464</v>
+        <v>0.2816</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8253</v>
+        <v>-0.9194</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.194</v>
+        <v>-0.0764</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6313</v>
+        <v>-0.8429</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2256</v>
@@ -1078,13 +1078,13 @@
         <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2116</v>
+        <v>0.1176</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2352</v>
+        <v>-0.1176</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4468</v>
+        <v>0.2352</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7653</v>
+        <v>-1.4851</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4618</v>
+        <v>-2.2082</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6966</v>
+        <v>0.723</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3389</v>
@@ -1156,13 +1156,13 @@
         <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2528</v>
+        <v>0.5329</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0559</v>
+        <v>0.1978</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3087</v>
+        <v>0.3351</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2452</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7523</v>
+        <v>-3.6406</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1228</v>
+        <v>-3.064</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.5766</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7309</v>
@@ -1234,13 +1234,13 @@
         <v>0.5661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1534</v>
+        <v>-0.0417</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3527</v>
+        <v>-0.2939</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1993</v>
+        <v>0.2522</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6036</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1685</v>
+        <v>-3.6611</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5141</v>
+        <v>-5.0068</v>
       </c>
       <c r="F11" t="n">
         <v>1.3456</v>
@@ -1312,10 +1312,10 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1793</v>
+        <v>0.3281</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0582</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="U11" t="n">
         <v>0.8789</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7443</v>
+        <v>-5.3319</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.373</v>
+        <v>-7.1193</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6286</v>
+        <v>1.7874</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3655</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0935</v>
+        <v>0.5059</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4674</v>
+        <v>-0.2137</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5609</v>
+        <v>0.7196</v>
       </c>
       <c r="V12" t="n">
         <v>1.2452</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7094</v>
+        <v>-4.1213</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.9453</v>
+        <v>-6.357399999999999</v>
       </c>
       <c r="F13" t="n">
         <v>2.236</v>
@@ -1468,13 +1468,13 @@
         <v>10.3785</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7072</v>
+        <v>3.2951</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9197</v>
+        <v>-1.3318</v>
       </c>
       <c r="U13" t="n">
-        <v>4.6268</v>
+        <v>4.626799999999999</v>
       </c>
       <c r="V13" t="n">
         <v>6.810600000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4523</v>
+        <v>6.7794</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4469</v>
+        <v>3.6417</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0054</v>
+        <v>3.1377</v>
       </c>
       <c r="G14" t="n">
         <v>4.7168</v>
@@ -1546,13 +1546,13 @@
         <v>2.8305</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4532</v>
+        <v>-0.1261</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9871</v>
+        <v>-0.7922</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.6661</v>
       </c>
       <c r="V14" t="n">
         <v>1.2452</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.367</v>
+        <v>1.6329</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2593</v>
+        <v>1.5516</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1078</v>
+        <v>0.0813</v>
       </c>
       <c r="G15" t="n">
         <v>3.7032</v>
@@ -1624,13 +1624,13 @@
         <v>2.6418</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9023</v>
+        <v>-0.6365</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9406</v>
+        <v>-0.6483</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0383</v>
+        <v>0.0118</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1886</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MARZIALI</t>
+          <t>S. SIDDIQUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.523</v>
+        <v>0.2481</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2093</v>
+        <v>0.8439</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7323</v>
+        <v>-0.5958</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6964</v>
+        <v>1.2107</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3757</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3207</v>
+        <v>0.5196</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2889</v>
+        <v>2.1804</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4867</v>
+        <v>1.3578</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.7756</v>
+        <v>0.8226</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4074</v>
+        <v>-0.9697</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>0.455</v>
+        <v>-0.303</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4531</v>
+        <v>1.3209</v>
       </c>
       <c r="S16" t="n">
-        <v>0.408</v>
+        <v>-0.1138</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2787</v>
+        <v>-0.393</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6867</v>
+        <v>0.2792</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3018</v>
+        <v>-1.2262</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0439</v>
+        <v>0.2304</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0528</v>
+        <v>-2.7605</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0966</v>
+        <v>2.9908</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3728</v>
@@ -1780,13 +1780,13 @@
         <v>3.3966</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7912</v>
+        <v>-0.6047</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1046</v>
+        <v>-0.8123</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3134</v>
+        <v>0.2076</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2452</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. SIDDIQUE</t>
+          <t>M. MARZIALI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0791</v>
+        <v>0.1513</v>
       </c>
       <c r="E18" t="n">
-        <v>0.649</v>
+        <v>-2.5016</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7281</v>
+        <v>2.6529</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2107</v>
+        <v>-1.6964</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.3757</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5196</v>
+        <v>-1.3207</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1804</v>
+        <v>-1.2889</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3578</v>
+        <v>0.4867</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8226</v>
+        <v>-1.7756</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9697</v>
+        <v>-0.4074</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.303</v>
+        <v>0.455</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3209</v>
+        <v>2.4531</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4409</v>
+        <v>0.0363</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5879</v>
+        <v>-0.571</v>
       </c>
       <c r="U18" t="n">
-        <v>0.147</v>
+        <v>0.6073</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2262</v>
+        <v>0.3018</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CLOSSET MARTINEZ</t>
+          <t>D. CAZORLA ZARAGOZI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4597</v>
+        <v>0.1498</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0804</v>
+        <v>-0.206</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3794</v>
+        <v>0.3557</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-1.7441</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0634</v>
+        <v>-0.4907</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8532</v>
+        <v>-1.2535</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.8925</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0477</v>
+        <v>-0.3749</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5503</v>
+        <v>-0.5177</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2873</v>
+        <v>-0.8516</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0157</v>
+        <v>-0.1158</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.303</v>
+        <v>-0.7358</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5661</v>
+        <v>2.4531</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5096</v>
+        <v>2.4531</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0658</v>
+        <v>-0.5592</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1205</v>
+        <v>-0.5587</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0546</v>
+        <v>-0.0005</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>1.2452</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.547</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>D. CLOSSET MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5666</v>
+        <v>-0.7785</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7883</v>
+        <v>-0.3727</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3548</v>
+        <v>-0.4058</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6857</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.151</v>
+        <v>0.0634</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5347</v>
+        <v>-0.8532</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1358</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2215</v>
+        <v>0.0477</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3573</v>
+        <v>-0.5503</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4501</v>
+        <v>-0.2873</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3725</v>
+        <v>0.0157</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8226</v>
+        <v>-0.303</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R20" t="n">
         <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3321</v>
+        <v>-0.2529</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6525</v>
+        <v>-0.1718</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3204</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.094</v>
+        <v>-0.3018</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.094</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. CAZORLA ZARAGOZI</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6284</v>
+        <v>-0.9699</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6932</v>
+        <v>-1.0987</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.1288</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7441</v>
+        <v>0.1182</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4907</v>
+        <v>-0.0117</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2535</v>
+        <v>0.1299</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8925</v>
+        <v>0.0211</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3749</v>
+        <v>0.0211</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5177</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8516</v>
+        <v>0.097</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1158</v>
+        <v>-0.0329</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7358</v>
+        <v>0.1299</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4531</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3374</v>
+        <v>-0.1446</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0458</v>
+        <v>-0.1764</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2915</v>
+        <v>0.0318</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-1.1957</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0987</v>
+        <v>1.1062</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2082</v>
+        <v>-2.3019</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1182</v>
+        <v>0.6857</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0117</v>
+        <v>0.151</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1299</v>
+        <v>0.5347</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0211</v>
+        <v>1.1358</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0211</v>
+        <v>-0.2215</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.3573</v>
       </c>
       <c r="M22" t="n">
-        <v>0.097</v>
+        <v>-0.4501</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0329</v>
+        <v>0.3725</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1299</v>
+        <v>-0.8226</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.297</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1764</v>
+        <v>-0.0296</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1111</v>
+        <v>-0.2674</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-3.094</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-3.094</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0526</v>
+        <v>-1.5384</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2451</v>
+        <v>-2.44</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1926</v>
+        <v>0.9016</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0394</v>
@@ -2248,13 +2248,13 @@
         <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4773</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2787</v>
+        <v>-0.4736</v>
       </c>
       <c r="U23" t="n">
-        <v>0.756</v>
+        <v>0.465</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3018</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.709200000000001</v>
+        <v>4.7094</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.236</v>
+        <v>-2.2361</v>
       </c>
       <c r="F24" t="n">
-        <v>6.9453</v>
+        <v>6.945300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>4.7921</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5199</v>
+        <v>2.519899999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>2.272</v>
+        <v>2.271999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>8.430200000000003</v>
@@ -2317,7 +2317,7 @@
         <v>-1.8383</v>
       </c>
       <c r="P24" t="n">
-        <v>9.434999999999999</v>
+        <v>9.435</v>
       </c>
       <c r="Q24" t="n">
         <v>-10.3785</v>
@@ -2326,10 +2326,10 @@
         <v>19.8135</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.706999999999999</v>
+        <v>-2.707000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.626799999999999</v>
+        <v>-4.626900000000001</v>
       </c>
       <c r="U24" t="n">
         <v>1.9198</v>
